--- a/ajorat.xlsx
+++ b/ajorat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\files (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86A9CC1-2E73-4B2A-86EF-4D64B18F143D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B1E62E-48D5-43BE-9A49-F300A2E5BE26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="521">
   <si>
     <t>نام ساخته</t>
   </si>
@@ -885,10 +885,709 @@
     <t>کریستال آزادی</t>
   </si>
   <si>
-    <t>تست</t>
-  </si>
-  <si>
     <t>کارجور</t>
+  </si>
+  <si>
+    <t>اراز دیور</t>
+  </si>
+  <si>
+    <t>نیم ست</t>
+  </si>
+  <si>
+    <t>ارزو واوک</t>
+  </si>
+  <si>
+    <t>افاق</t>
+  </si>
+  <si>
+    <t>الهیه</t>
+  </si>
+  <si>
+    <t>الیزه</t>
+  </si>
+  <si>
+    <t>انا گلد جی کالر</t>
+  </si>
+  <si>
+    <t>ایوا لاوین</t>
+  </si>
+  <si>
+    <t>اکسترا ویولت</t>
+  </si>
+  <si>
+    <t>بهار بچگانه</t>
+  </si>
+  <si>
+    <t>پولکی لارا</t>
+  </si>
+  <si>
+    <t>توپک 1360</t>
+  </si>
+  <si>
+    <t>ثمین زر ایران</t>
+  </si>
+  <si>
+    <t>چاکی</t>
+  </si>
+  <si>
+    <t>دوبال</t>
+  </si>
+  <si>
+    <t>دوچرخه ااس</t>
+  </si>
+  <si>
+    <t>دیولو</t>
+  </si>
+  <si>
+    <t>رزا پرنس</t>
+  </si>
+  <si>
+    <t>رژنیان</t>
+  </si>
+  <si>
+    <t>رویا زاوی</t>
+  </si>
+  <si>
+    <t>رویال اوا</t>
+  </si>
+  <si>
+    <t>ساویرون 2069</t>
+  </si>
+  <si>
+    <t>شهریار</t>
+  </si>
+  <si>
+    <t>صدف مهرسان</t>
+  </si>
+  <si>
+    <t>طرح اوا</t>
+  </si>
+  <si>
+    <t>گلد اوا</t>
+  </si>
+  <si>
+    <t>نور</t>
+  </si>
+  <si>
+    <t>نورسان</t>
+  </si>
+  <si>
+    <t>هرمس 1241</t>
+  </si>
+  <si>
+    <t>واوک</t>
+  </si>
+  <si>
+    <t>ون کلیف ااس</t>
+  </si>
+  <si>
+    <t>ون کلیف ازادی</t>
+  </si>
+  <si>
+    <t>ون کلیف تراش</t>
+  </si>
+  <si>
+    <t>مدال</t>
+  </si>
+  <si>
+    <t>اره لیزری</t>
+  </si>
+  <si>
+    <t>الیزابت</t>
+  </si>
+  <si>
+    <t>اماتیس</t>
+  </si>
+  <si>
+    <t>ایران چهار باغ</t>
+  </si>
+  <si>
+    <t>تابان زر ایران</t>
+  </si>
+  <si>
+    <t>تاج گلد تهران تاج</t>
+  </si>
+  <si>
+    <t>حروف</t>
+  </si>
+  <si>
+    <t>حروف چهارباغ</t>
+  </si>
+  <si>
+    <t>حروف قوی</t>
+  </si>
+  <si>
+    <t>دلبر دلاریس 1548</t>
+  </si>
+  <si>
+    <t>دم وال</t>
+  </si>
+  <si>
+    <t>رامو اورتگا</t>
+  </si>
+  <si>
+    <t>سه بعدی 1587</t>
+  </si>
+  <si>
+    <t>شیر خورشید دیاموند</t>
+  </si>
+  <si>
+    <t>فروهر لیزری</t>
+  </si>
+  <si>
+    <t>قلب الهیه</t>
+  </si>
+  <si>
+    <t>قلب مسی اینه ای</t>
+  </si>
+  <si>
+    <t>لارا دوقاب 1642</t>
+  </si>
+  <si>
+    <t>لیزری درین</t>
+  </si>
+  <si>
+    <t>لیلیوم 1587</t>
+  </si>
+  <si>
+    <t>مارکو</t>
+  </si>
+  <si>
+    <t>مهرگلد 1199</t>
+  </si>
+  <si>
+    <t>نایس دلاریس 1548</t>
+  </si>
+  <si>
+    <t>هخامنش</t>
+  </si>
+  <si>
+    <t>ورساچ اهو</t>
+  </si>
+  <si>
+    <t>ورساچ لوییس</t>
+  </si>
+  <si>
+    <t>ورساچه لوکس</t>
+  </si>
+  <si>
+    <t>ورساچی 1111</t>
+  </si>
+  <si>
+    <t>وی گلد</t>
+  </si>
+  <si>
+    <t>وی گلد ایران</t>
+  </si>
+  <si>
+    <t>وی گلد رز</t>
+  </si>
+  <si>
+    <t>مونارا - 1,000,000 ریال</t>
+  </si>
+  <si>
+    <t>گوشواره</t>
+  </si>
+  <si>
+    <t>اریانا 1011</t>
+  </si>
+  <si>
+    <t>اریانا 1012</t>
+  </si>
+  <si>
+    <t>المپیک</t>
+  </si>
+  <si>
+    <t>امگا سوپر 1841</t>
+  </si>
+  <si>
+    <t>ایفل</t>
+  </si>
+  <si>
+    <t>پروفیل کارتیه</t>
+  </si>
+  <si>
+    <t>ترمه</t>
+  </si>
+  <si>
+    <t>توپی لوکس</t>
+  </si>
+  <si>
+    <t>حلقه ای</t>
+  </si>
+  <si>
+    <t>حلقه ای سوبل رنگی</t>
+  </si>
+  <si>
+    <t>حلقه ای ماه و ستاره</t>
+  </si>
+  <si>
+    <t>حلقه تراش</t>
+  </si>
+  <si>
+    <t>حلقه رنگی</t>
+  </si>
+  <si>
+    <t>دنیز گوی</t>
+  </si>
+  <si>
+    <t>دوبل اویز</t>
+  </si>
+  <si>
+    <t>دوراتو 1815</t>
+  </si>
+  <si>
+    <t>راحیل1999</t>
+  </si>
+  <si>
+    <t>سیلور</t>
+  </si>
+  <si>
+    <t>شانل پوپک</t>
+  </si>
+  <si>
+    <t>شانل مشکل گشا</t>
+  </si>
+  <si>
+    <t>شانل 1319</t>
+  </si>
+  <si>
+    <t>صدفی 1317</t>
+  </si>
+  <si>
+    <t>صدفی پرتراش</t>
+  </si>
+  <si>
+    <t>صدفی طرح نرمال</t>
+  </si>
+  <si>
+    <t>فندقی</t>
+  </si>
+  <si>
+    <t>فیلیپ</t>
+  </si>
+  <si>
+    <t>قلب اپل</t>
+  </si>
+  <si>
+    <t>گوی حلقه ای</t>
+  </si>
+  <si>
+    <t>گوی منجوقی</t>
+  </si>
+  <si>
+    <t>لول تراش شمش بار</t>
+  </si>
+  <si>
+    <t>مات ضربه</t>
+  </si>
+  <si>
+    <t>ماه</t>
+  </si>
+  <si>
+    <t>محدب</t>
+  </si>
+  <si>
+    <t>ملیله</t>
+  </si>
+  <si>
+    <t>موزی</t>
+  </si>
+  <si>
+    <t>میخی ایسان</t>
+  </si>
+  <si>
+    <t>میخی ون کلیف</t>
+  </si>
+  <si>
+    <t>نیل</t>
+  </si>
+  <si>
+    <t>هندسی</t>
+  </si>
+  <si>
+    <t>کارتیه 257</t>
+  </si>
+  <si>
+    <t>کلکته</t>
+  </si>
+  <si>
+    <t>کلکته قلبی</t>
+  </si>
+  <si>
+    <t>کلکته هندی</t>
+  </si>
+  <si>
+    <t>اینه ای ونزو</t>
+  </si>
+  <si>
+    <t>ابگینه انگشتر شنی</t>
+  </si>
+  <si>
+    <t>اذر</t>
+  </si>
+  <si>
+    <t>پلاک دست یک گرمی</t>
+  </si>
+  <si>
+    <t>تیفانی اسمان</t>
+  </si>
+  <si>
+    <t>دوریکا رز</t>
+  </si>
+  <si>
+    <t>بی ان جی</t>
+  </si>
+  <si>
+    <t>دوریکا</t>
+  </si>
+  <si>
+    <t>ابگینه صدف نیلوفر</t>
+  </si>
+  <si>
+    <t>کیتی</t>
+  </si>
+  <si>
+    <t>پیرسینگ</t>
+  </si>
+  <si>
+    <t>مدبر 400 سوتی</t>
+  </si>
+  <si>
+    <t>مدبر 200 سوتی</t>
+  </si>
+  <si>
+    <t>ساعت</t>
+  </si>
+  <si>
+    <t>پلاس</t>
+  </si>
+  <si>
+    <t>مدبر 250 سوتی</t>
+  </si>
+  <si>
+    <t>پیرسینگ اسپرلوس</t>
+  </si>
+  <si>
+    <t>سرویس</t>
+  </si>
+  <si>
+    <t>احسان گلد</t>
+  </si>
+  <si>
+    <t>الیزابت گشنیزی</t>
+  </si>
+  <si>
+    <t>امرال اتمی</t>
+  </si>
+  <si>
+    <t>ایسان کسر نگین</t>
+  </si>
+  <si>
+    <t>پنج شیر</t>
+  </si>
+  <si>
+    <t>شانل صدف</t>
+  </si>
+  <si>
+    <t>طنابی پنبه 236</t>
+  </si>
+  <si>
+    <t>طنابی درشت</t>
+  </si>
+  <si>
+    <t>طنابی 1515</t>
+  </si>
+  <si>
+    <t>گلباز رزگلد سفید</t>
+  </si>
+  <si>
+    <t>گندم سوپر</t>
+  </si>
+  <si>
+    <t>گوی زرین</t>
+  </si>
+  <si>
+    <t>نایجل</t>
+  </si>
+  <si>
+    <t>کارتیر پلاس</t>
+  </si>
+  <si>
+    <t>کاترین</t>
+  </si>
+  <si>
+    <t>کارتیه ترمه</t>
+  </si>
+  <si>
+    <t>کارتیه دوبل 82</t>
+  </si>
+  <si>
+    <t>کرون</t>
+  </si>
+  <si>
+    <t>گوی گلبهار</t>
+  </si>
+  <si>
+    <t>بنی طوق تراش</t>
+  </si>
+  <si>
+    <t>دوشز</t>
+  </si>
+  <si>
+    <t>شهرزاد</t>
+  </si>
+  <si>
+    <t>تیفانی شهرزاد</t>
+  </si>
+  <si>
+    <t>مروارید دایانا</t>
+  </si>
+  <si>
+    <t>مانیسا</t>
+  </si>
+  <si>
+    <t>کارتیه پفکی 1170</t>
+  </si>
+  <si>
+    <t>شانل پیمان</t>
+  </si>
+  <si>
+    <t>تیفانی نگین سوپر</t>
+  </si>
+  <si>
+    <t>الدرادو</t>
+  </si>
+  <si>
+    <t>تراش قوی</t>
+  </si>
+  <si>
+    <t>محیا گلد</t>
+  </si>
+  <si>
+    <t>شراره درین</t>
+  </si>
+  <si>
+    <t>تراش سفید قوی</t>
+  </si>
+  <si>
+    <t>پرشیا 1643</t>
+  </si>
+  <si>
+    <t>ارغوان</t>
+  </si>
+  <si>
+    <t>گول عسل</t>
+  </si>
+  <si>
+    <t>ون کلیف نانو</t>
+  </si>
+  <si>
+    <t>شانل تکنو 90</t>
+  </si>
+  <si>
+    <t>تیفانی تبریز</t>
+  </si>
+  <si>
+    <t>دوشز نگین دار</t>
+  </si>
+  <si>
+    <t>ون کلیف ارجی</t>
+  </si>
+  <si>
+    <t>الینا درین</t>
+  </si>
+  <si>
+    <t>لوکس اسلیمی 624</t>
+  </si>
+  <si>
+    <t>ون کلیف گلدن</t>
+  </si>
+  <si>
+    <t>ون کلیف دوجی</t>
+  </si>
+  <si>
+    <t>کارتیه فشن 406</t>
+  </si>
+  <si>
+    <t>کارتیر 159</t>
+  </si>
+  <si>
+    <t>البرنادو سهند</t>
+  </si>
+  <si>
+    <t>ون کلیف همایون</t>
+  </si>
+  <si>
+    <t>ون کلیف مینیمال همایون</t>
+  </si>
+  <si>
+    <t>بابونه دیولو</t>
+  </si>
+  <si>
+    <t>شانل قوی</t>
+  </si>
+  <si>
+    <t>مهر قوی</t>
+  </si>
+  <si>
+    <t>بهسا زر2119</t>
+  </si>
+  <si>
+    <t>بیروتی ss</t>
+  </si>
+  <si>
+    <t>دیسکو</t>
+  </si>
+  <si>
+    <t>دیسکو 5 صفر</t>
+  </si>
+  <si>
+    <t>طنابی سوپر 1213</t>
+  </si>
+  <si>
+    <t>قلمدون</t>
+  </si>
+  <si>
+    <t>ورساچی مردانه دو رنگ</t>
+  </si>
+  <si>
+    <t>کارتیه سوپر 257</t>
+  </si>
+  <si>
+    <t>طنابی E39</t>
+  </si>
+  <si>
+    <t>پولکی اکسترا</t>
+  </si>
+  <si>
+    <t>کلاف</t>
+  </si>
+  <si>
+    <t>کارتیه ریز ابریشم</t>
+  </si>
+  <si>
+    <t>ونزی 80</t>
+  </si>
+  <si>
+    <t>طنابی رز گلد</t>
+  </si>
+  <si>
+    <t>کارتیه بیتا سوپر</t>
+  </si>
+  <si>
+    <t>کارتیه 401</t>
+  </si>
+  <si>
+    <t>یزدی جور</t>
+  </si>
+  <si>
+    <t>هرینگ بن</t>
+  </si>
+  <si>
+    <t>میرو</t>
+  </si>
+  <si>
+    <t>طنابی 1113 دورنگ</t>
+  </si>
+  <si>
+    <t>زیرو</t>
+  </si>
+  <si>
+    <t>قلمدون سوتی</t>
+  </si>
+  <si>
+    <t>پرسپولیس</t>
+  </si>
+  <si>
+    <t>قلمدون سوتی سفید</t>
+  </si>
+  <si>
+    <t>هل گلاب</t>
+  </si>
+  <si>
+    <t>تیغ ماهی ( نفرتیتی )</t>
+  </si>
+  <si>
+    <t>فیگارو 401</t>
+  </si>
+  <si>
+    <t>میرو سوپر سوتی</t>
+  </si>
+  <si>
+    <t>کارتیه دوبل ژاپنی</t>
+  </si>
+  <si>
+    <t>کارتیه 1752</t>
+  </si>
+  <si>
+    <t>درین میلانو</t>
+  </si>
+  <si>
+    <t>فیگارو پلاس</t>
+  </si>
+  <si>
+    <t>طنابی 1094</t>
+  </si>
+  <si>
+    <t>کارتیه لوزی</t>
+  </si>
+  <si>
+    <t>پولکی 472</t>
+  </si>
+  <si>
+    <t>کراتیر 472</t>
+  </si>
+  <si>
+    <t>فلامینگو 472</t>
+  </si>
+  <si>
+    <t>فلامینگو 50</t>
+  </si>
+  <si>
+    <t>سوپر لایت گلستانه</t>
+  </si>
+  <si>
+    <t>طنابی دورنگ 1253</t>
+  </si>
+  <si>
+    <t>طنابی کونیک</t>
+  </si>
+  <si>
+    <t>قلمدون کاغذی</t>
+  </si>
+  <si>
+    <t>اوان 1837</t>
+  </si>
+  <si>
+    <t>مردانه همایون 472</t>
+  </si>
+  <si>
+    <t>ونزی 1811</t>
+  </si>
+  <si>
+    <t>پرسپولیس سوپر</t>
+  </si>
+  <si>
+    <t>رولو سوتی</t>
+  </si>
+  <si>
+    <t>بیزمارک 588</t>
+  </si>
+  <si>
+    <t>کارتیه ریز 65</t>
+  </si>
+  <si>
+    <t>اپل قلمدون</t>
+  </si>
+  <si>
+    <t>دیپلمات پویان 1719</t>
+  </si>
+  <si>
+    <t>کارتیه 1719</t>
+  </si>
+  <si>
+    <t>زنجیر</t>
   </si>
 </sst>
 </file>
@@ -1271,7 +1970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C285"/>
+  <dimension ref="A1:C522"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="9" customWidth="1"/>
@@ -4404,18 +5103,2626 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" s="9" t="s">
+    <row r="285" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A285" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B285" s="6">
+        <v>10</v>
+      </c>
+      <c r="C285" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A286" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B286" s="6">
+        <v>12.5</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A287" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B287" s="6">
+        <v>5</v>
+      </c>
+      <c r="C287" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A288" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B288" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="C288" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A289" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B289" s="6">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A290" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B290" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="C290" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A291" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B291" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="C291" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A292" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B292" s="6">
+        <v>8</v>
+      </c>
+      <c r="C292" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A293" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B293" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A294" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B294" s="6">
+        <v>10.9</v>
+      </c>
+      <c r="C294" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A295" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B295" s="6">
+        <v>6</v>
+      </c>
+      <c r="C295" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A296" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="B296" s="6">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="C296" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A297" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B297" s="6">
+        <v>7</v>
+      </c>
+      <c r="C297" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A298" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B298" s="6">
+        <v>7</v>
+      </c>
+      <c r="C298" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A299" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B299" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="C299" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A300" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B300" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="C300" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A301" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B301" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="C301" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A302" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="B302" s="6">
+        <v>11.5</v>
+      </c>
+      <c r="C302" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A303" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B303" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="C303" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A304" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B304" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="C304" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A305" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="B305" s="6">
+        <v>10</v>
+      </c>
+      <c r="C305" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A306" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B306" s="6">
+        <v>11</v>
+      </c>
+      <c r="C306" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A307" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B307" s="6">
+        <v>7.8</v>
+      </c>
+      <c r="C307" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A308" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B308" s="6">
+        <v>11</v>
+      </c>
+      <c r="C308" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A309" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B309" s="6">
+        <v>12</v>
+      </c>
+      <c r="C309" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A310" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="B310" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="C310" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A311" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="B311" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="C311" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A312" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B312" s="6">
+        <v>14</v>
+      </c>
+      <c r="C312" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A313" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="B313" s="6">
+        <v>4</v>
+      </c>
+      <c r="C313" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A314" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B314" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="C314" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A315" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B315" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="C315" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A316" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="B316" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="C316" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A317" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B317" s="6">
+        <v>11</v>
+      </c>
+      <c r="C317" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A318" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B318" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="C318" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B319" s="10">
+        <v>5</v>
+      </c>
+      <c r="C319" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="B320" s="10">
+        <v>12</v>
+      </c>
+      <c r="C320" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B321" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="C321" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B322" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="C322" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B323" s="10">
+        <v>7</v>
+      </c>
+      <c r="C323" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B324" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="C324" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B325" s="10">
+        <v>11.5</v>
+      </c>
+      <c r="C325" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B326" s="10">
+        <v>9</v>
+      </c>
+      <c r="C326" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="B327" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="C327" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="B328" s="10">
+        <v>8</v>
+      </c>
+      <c r="C328" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B329" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="C329" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="B330" s="10">
+        <v>7</v>
+      </c>
+      <c r="C330" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="B331" s="10">
+        <v>12</v>
+      </c>
+      <c r="C331" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="B332" s="10">
+        <v>11</v>
+      </c>
+      <c r="C332" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="B333" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C333" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B334" s="10">
+        <v>12.5</v>
+      </c>
+      <c r="C334" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="B335" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="C335" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B336" s="10">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="C336" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B337" s="10">
+        <v>5</v>
+      </c>
+      <c r="C337" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B338" s="10">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="C338" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="B339" s="10">
+        <v>7</v>
+      </c>
+      <c r="C339" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B340" s="10">
+        <v>6</v>
+      </c>
+      <c r="C340" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="B341" s="10">
+        <v>10.8</v>
+      </c>
+      <c r="C341" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B342" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C342" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="B343" s="10">
+        <v>10</v>
+      </c>
+      <c r="C343" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="B344" s="10">
+        <v>10</v>
+      </c>
+      <c r="C344" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B345" s="10">
+        <v>9.5</v>
+      </c>
+      <c r="C345" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="B346" s="10">
+        <v>12</v>
+      </c>
+      <c r="C346" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B347" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="C347" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="B348" s="10">
+        <v>8</v>
+      </c>
+      <c r="C348" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B349" s="10">
+        <v>6</v>
+      </c>
+      <c r="C349" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="B350" s="10">
+        <v>7</v>
+      </c>
+      <c r="C350" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="B351" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C351" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="B352" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C352" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B353" s="10">
+        <v>12.5</v>
+      </c>
+      <c r="C353" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="B354" s="10">
+        <v>11</v>
+      </c>
+      <c r="C354" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="B355" s="10">
+        <v>11</v>
+      </c>
+      <c r="C355" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="B356" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="C356" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B357" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="C357" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B358" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C358" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B359" s="10">
+        <v>7.7</v>
+      </c>
+      <c r="C359" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="B360" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="C360" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="B361" s="10">
+        <v>5</v>
+      </c>
+      <c r="C361" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="B362" s="10">
+        <v>11.5</v>
+      </c>
+      <c r="C362" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="B363" s="10">
+        <v>5</v>
+      </c>
+      <c r="C363" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="B364" s="10">
+        <v>5</v>
+      </c>
+      <c r="C364" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B365" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="C365" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="B366" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C366" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="B367" s="10">
+        <v>8</v>
+      </c>
+      <c r="C367" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="B368" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="C368" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="B369" s="10">
+        <v>7.9</v>
+      </c>
+      <c r="C369" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="B370" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="C370" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B371" s="10">
+        <v>7</v>
+      </c>
+      <c r="C371" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B372" s="10">
+        <v>4.8</v>
+      </c>
+      <c r="C372" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B373" s="10">
+        <v>6</v>
+      </c>
+      <c r="C373" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="B374" s="10">
+        <v>5</v>
+      </c>
+      <c r="C374" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B375" s="10">
+        <v>4.7</v>
+      </c>
+      <c r="C375" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="B376" s="10">
+        <v>5.3</v>
+      </c>
+      <c r="C376" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B377" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="C377" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="B378" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="C378" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="B379" s="10">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="C379" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="B380" s="10">
+        <v>6.2</v>
+      </c>
+      <c r="C380" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="B381" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C381" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="B382" s="10">
+        <v>7.7</v>
+      </c>
+      <c r="C382" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="B383" s="10">
+        <v>5.3</v>
+      </c>
+      <c r="C383" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="B384" s="10">
+        <v>5</v>
+      </c>
+      <c r="C384" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="B385" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C385" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B386" s="10">
+        <v>6</v>
+      </c>
+      <c r="C386" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="B387" s="10">
+        <v>5.2</v>
+      </c>
+      <c r="C387" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="B388" s="10">
+        <v>14.5</v>
+      </c>
+      <c r="C388" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="B389" s="10">
+        <v>13</v>
+      </c>
+      <c r="C389" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="B390" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="C390" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="B391" s="10">
+        <v>5</v>
+      </c>
+      <c r="C391" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B392" s="10">
+        <v>6</v>
+      </c>
+      <c r="C392" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="B393" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="C393" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="B394" s="10">
+        <v>3.7</v>
+      </c>
+      <c r="C394" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B395" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="C395" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="B396" s="10">
+        <v>10</v>
+      </c>
+      <c r="C396" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="B397" s="10">
+        <v>16.8</v>
+      </c>
+      <c r="C397" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="B285" s="10">
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="B398" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="C398" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="B399" s="10">
+        <v>7.3</v>
+      </c>
+      <c r="C399" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="B400" s="10">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="C400" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B401" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C401" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B402" s="10">
+        <v>23.5</v>
+      </c>
+      <c r="C402" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="B403" s="10">
+        <v>11.1</v>
+      </c>
+      <c r="C403" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="B404" s="10">
+        <v>19.8</v>
+      </c>
+      <c r="C404" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="B405" s="10">
+        <v>13</v>
+      </c>
+      <c r="C405" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="B406" s="10">
+        <v>14</v>
+      </c>
+      <c r="C406" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="B407" s="10">
+        <v>-5</v>
+      </c>
+      <c r="C407" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="B408" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C408" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="B409" s="10">
+        <v>20</v>
+      </c>
+      <c r="C409" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B410" s="10">
+        <v>16.5</v>
+      </c>
+      <c r="C410" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="B411" s="10">
+        <v>0</v>
+      </c>
+      <c r="C411" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="B412" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="C412" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B413" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="C413" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="B414" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="C414" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="B415" s="10">
+        <v>9.5</v>
+      </c>
+      <c r="C415" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="B416" s="10">
+        <v>13.5</v>
+      </c>
+      <c r="C416" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A417" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B417" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="C417" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A418" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B418" s="10">
+        <v>5</v>
+      </c>
+      <c r="C418" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A419" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B419" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="C419" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A420" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="B420" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="C420" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A421" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="B421" s="10">
+        <v>5</v>
+      </c>
+      <c r="C421" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A422" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="B422" s="10">
+        <v>7</v>
+      </c>
+      <c r="C422" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A423" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="B423" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="C423" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A424" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="B424" s="10">
+        <v>7.8</v>
+      </c>
+      <c r="C424" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="B425" s="10">
+        <v>5</v>
+      </c>
+      <c r="C425" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A426" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="B426" s="10">
+        <v>10</v>
+      </c>
+      <c r="C426" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A427" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="B427" s="10">
+        <v>9.5</v>
+      </c>
+      <c r="C427" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A428" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="B428" s="10">
+        <v>9</v>
+      </c>
+      <c r="C428" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A429" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="B429" s="10">
+        <v>12</v>
+      </c>
+      <c r="C429" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A430" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B430" s="10">
+        <v>5</v>
+      </c>
+      <c r="C430" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A431" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="B431" s="10">
+        <v>14.3</v>
+      </c>
+      <c r="C431" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A432" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="B432" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="C432" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B433" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C433" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B434" s="10">
+        <v>8</v>
+      </c>
+      <c r="C434" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="B435" s="10">
+        <v>12</v>
+      </c>
+      <c r="C435" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A436" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B436" s="10">
+        <v>5</v>
+      </c>
+      <c r="C436" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A437" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="B437" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="C437" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A438" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B438" s="10">
+        <v>4.7</v>
+      </c>
+      <c r="C438" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A439" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="B439" s="10">
+        <v>13</v>
+      </c>
+      <c r="C439" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A440" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B440" s="10">
+        <v>4</v>
+      </c>
+      <c r="C440" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A441" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="B441" s="10">
+        <v>6</v>
+      </c>
+      <c r="C441" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A442" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="B442" s="10">
+        <v>10</v>
+      </c>
+      <c r="C442" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A443" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="B443" s="10">
+        <v>18</v>
+      </c>
+      <c r="C443" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A444" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="B444" s="10">
+        <v>13</v>
+      </c>
+      <c r="C444" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A445" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="B445" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="C445" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A446" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="B446" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C446" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="B447" s="10">
+        <v>9</v>
+      </c>
+      <c r="C447" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A448" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="B448" s="10">
+        <v>7</v>
+      </c>
+      <c r="C448" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A449" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="B449" s="10">
+        <v>13.5</v>
+      </c>
+      <c r="C449" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A450" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="B450" s="10">
+        <v>9.5</v>
+      </c>
+      <c r="C450" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A451" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="B451" s="10">
+        <v>16</v>
+      </c>
+      <c r="C451" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A452" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B452" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="C452" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A453" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="B453" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="C453" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A454" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="B454" s="10">
+        <v>8</v>
+      </c>
+      <c r="C454" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A455" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="B455" s="10">
+        <v>11.7</v>
+      </c>
+      <c r="C455" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A456" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B456" s="10">
+        <v>7.7</v>
+      </c>
+      <c r="C456" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A457" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="B457" s="10">
+        <v>6</v>
+      </c>
+      <c r="C457" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A458" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B458" s="10">
+        <v>11.5</v>
+      </c>
+      <c r="C458" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A459" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="B459" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C459" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A460" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="B460" s="10">
+        <v>4</v>
+      </c>
+      <c r="C460" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A461" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="B461" s="10">
+        <v>6</v>
+      </c>
+      <c r="C461" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A462" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="B462" s="10">
+        <v>7</v>
+      </c>
+      <c r="C462" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A463" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="B463" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C463" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A464" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="B464" s="10">
+        <v>7</v>
+      </c>
+      <c r="C464" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A465" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B465" s="10">
+        <v>8</v>
+      </c>
+      <c r="C465" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A466" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="B466" s="10">
+        <v>9.5</v>
+      </c>
+      <c r="C466" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A467" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="B467" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="C467" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="B468" s="10">
+        <v>10</v>
+      </c>
+      <c r="C468" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A469" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="B469" s="10">
+        <v>10.3</v>
+      </c>
+      <c r="C469" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A470" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="B470" s="10">
+        <v>6</v>
+      </c>
+      <c r="C470" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A471" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B471" s="10">
+        <v>5</v>
+      </c>
+      <c r="C471" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A472" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="B472" s="10">
+        <v>7</v>
+      </c>
+      <c r="C472" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A473" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B473" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="C473" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A474" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B474" s="10">
+        <v>6.3</v>
+      </c>
+      <c r="C474" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A475" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="B475" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="C475" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A476" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="B476" s="10">
+        <v>5</v>
+      </c>
+      <c r="C476" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A477" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="B477" s="10">
+        <v>10</v>
+      </c>
+      <c r="C477" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A478" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="B478" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="C478" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A479" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="B479" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="C479" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480" s="9">
+        <v>226</v>
+      </c>
+      <c r="B480" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="C480" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="B481" s="10">
+        <v>7</v>
+      </c>
+      <c r="C481" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="B482" s="10">
+        <v>5</v>
+      </c>
+      <c r="C482" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="B483" s="10">
+        <v>6.3</v>
+      </c>
+      <c r="C483" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="B484" s="10">
+        <v>6.2</v>
+      </c>
+      <c r="C484" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="B485" s="10">
+        <v>5</v>
+      </c>
+      <c r="C485" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="B486" s="10">
+        <v>4.8</v>
+      </c>
+      <c r="C486" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A487" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="B487" s="10">
         <v>15</v>
       </c>
-      <c r="C285" s="11" t="s">
-        <v>287</v>
+      <c r="C487" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A488" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="B488" s="10">
+        <v>11.5</v>
+      </c>
+      <c r="C488" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A489" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B489" s="10">
+        <v>17.5</v>
+      </c>
+      <c r="C489" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A490" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="B490" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="C490" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A491" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="B491" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C491" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A492" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="B492" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="C492" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A493" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B493" s="10">
+        <v>8</v>
+      </c>
+      <c r="C493" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A494" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="B494" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C494" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A495" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B495" s="10">
+        <v>11</v>
+      </c>
+      <c r="C495" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A496" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="B496" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="C496" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A497" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="B497" s="10">
+        <v>22</v>
+      </c>
+      <c r="C497" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A498" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="B498" s="10">
+        <v>12.5</v>
+      </c>
+      <c r="C498" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A499" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="B499" s="10">
+        <v>5.3</v>
+      </c>
+      <c r="C499" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A500" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="B500" s="10">
+        <v>9</v>
+      </c>
+      <c r="C500" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A501" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="B501" s="10">
+        <v>14</v>
+      </c>
+      <c r="C501" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A502" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="B502" s="10">
+        <v>5.7</v>
+      </c>
+      <c r="C502" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A503" s="9">
+        <v>1719</v>
+      </c>
+      <c r="B503" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="C503" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A504" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="B504" s="10">
+        <v>14.5</v>
+      </c>
+      <c r="C504" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A505" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="B505" s="10">
+        <v>8</v>
+      </c>
+      <c r="C505" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A506" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="B506" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="C506" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A507" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="B507" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C507" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A508" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="B508" s="10">
+        <v>11.5</v>
+      </c>
+      <c r="C508" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A509" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="B509" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C509" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A510" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="B510" s="10">
+        <v>7.8</v>
+      </c>
+      <c r="C510" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A511" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="B511" s="10">
+        <v>14</v>
+      </c>
+      <c r="C511" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A512" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="B512" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="C512" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A513" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="B513" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="C513" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A514" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="B514" s="10">
+        <v>9</v>
+      </c>
+      <c r="C514" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A515" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="B515" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="C515" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A516" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B516" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="C516" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A517" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="B517" s="10">
+        <v>11</v>
+      </c>
+      <c r="C517" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A518" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="B518" s="10">
+        <v>5.7</v>
+      </c>
+      <c r="C518" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A519" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="B519" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="C519" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A520" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="B520" s="10">
+        <v>4.7</v>
+      </c>
+      <c r="C520" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A521" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="B521" s="10">
+        <v>5.3</v>
+      </c>
+      <c r="C521" s="11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A522" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="B522" s="10">
+        <v>5.3</v>
+      </c>
+      <c r="C522" s="11" t="s">
+        <v>520</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>